--- a/public/exports/69116418.xlsx
+++ b/public/exports/69116418.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166039</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183354</t>
+          <t xml:space="preserve">311183402</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9304,12 +9304,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9379,12 +9379,12 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9454,12 +9454,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports/69116418.xlsx
+++ b/public/exports/69116418.xlsx
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Voldgade 19A</t>
+          <t xml:space="preserve">Thygesminde Allé 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8635786</t>
+          <t xml:space="preserve">100046399</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="J34">
-        <v>594</v>
+        <v>1047</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246391</t>
+          <t xml:space="preserve">200061734</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-25</t>
+          <t xml:space="preserve">2022-09-06</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygesminde Allé 1</t>
+          <t xml:space="preserve">Vesterballevej 5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046399</t>
+          <t xml:space="preserve">9560002</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="J35">
-        <v>1047</v>
+        <v>2980</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200061734</t>
+          <t xml:space="preserve">310027405</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-06</t>
+          <t xml:space="preserve">2023-02-28</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterballevej 5</t>
+          <t xml:space="preserve">Thygesminde Allé 3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,30 +2676,30 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560002</t>
+          <t xml:space="preserve">100046399</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
-        <v>2980</v>
+        <v>3488</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">310027405</t>
+          <t xml:space="preserve">310035305</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Kuben Management A/S</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-28</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygesminde Allé 3</t>
+          <t xml:space="preserve">Hannerup Brovej 9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,30 +2751,30 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046399</t>
+          <t xml:space="preserve">738033, 5670622</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>3488</v>
+        <v>561</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035305</t>
+          <t xml:space="preserve">311010183</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuben Management A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2023-07-28</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannerup Brovej 9</t>
+          <t xml:space="preserve">Havepladsvej 177A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,30 +2826,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">738033, 5670622</t>
+          <t xml:space="preserve">5666167</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J38">
-        <v>561</v>
+        <v>1413</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311010183</t>
+          <t xml:space="preserve">311147951</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">NiH Energy ApS</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-28</t>
+          <t xml:space="preserve">2025-11-30</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 177A</t>
+          <t xml:space="preserve">Chr. Winthers Vej 44</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,30 +2901,30 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666167</t>
+          <t xml:space="preserve">5668856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>1413</v>
+        <v>2508</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147951</t>
+          <t xml:space="preserve">311166041</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NiH Energy ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-30</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr. Winthers Vej 44</t>
+          <t xml:space="preserve">Skjoldborgsvej 25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J40">
-        <v>2508</v>
+        <v>1081</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3056,11 +3056,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J41">
-        <v>1081</v>
+        <v>416</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3131,11 +3131,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J42">
-        <v>416</v>
+        <v>705</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldborgsvej 25</t>
+          <t xml:space="preserve">Lollandsgade 2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,30 +3201,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668856</t>
+          <t xml:space="preserve">5664903</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>705</v>
+        <v>2050</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311172659</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-26</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsgade 2</t>
+          <t xml:space="preserve">Sjællandsgade 23A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664903</t>
+          <t xml:space="preserve">5663527</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>2050</v>
+        <v>1598</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172659</t>
+          <t xml:space="preserve">311173333</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-26</t>
+          <t xml:space="preserve">2026-04-28</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsgade 23A</t>
+          <t xml:space="preserve">Vejlevej 14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663527</t>
+          <t xml:space="preserve">5673192</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>1598</v>
+        <v>1257</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173333</t>
+          <t xml:space="preserve">311173332</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlevej 14</t>
+          <t xml:space="preserve">Bragesvej 7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5673192</t>
+          <t xml:space="preserve">5667534</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>1257</v>
+        <v>755</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311173332</t>
+          <t xml:space="preserve">311176387</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-28</t>
+          <t xml:space="preserve">2026-05-13</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bragesvej 7</t>
+          <t xml:space="preserve">Bredstrupvej 41</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5667534</t>
+          <t xml:space="preserve">8506783</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="J47">
-        <v>755</v>
+        <v>976</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176387</t>
+          <t xml:space="preserve">311176386</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredstrupvej 41</t>
+          <t xml:space="preserve">Vendersgade 48</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8506783</t>
+          <t xml:space="preserve">5663424</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>976</v>
+        <v>509</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176386</t>
+          <t xml:space="preserve">311349007</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 48</t>
+          <t xml:space="preserve">Bissensvej 1A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663424</t>
+          <t xml:space="preserve">5671656</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>509</v>
+        <v>396</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349007</t>
+          <t xml:space="preserve">311176903</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-13</t>
+          <t xml:space="preserve">2026-05-17</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bissensvej 1A</t>
+          <t xml:space="preserve">Højmosevej 7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671656</t>
+          <t xml:space="preserve">4394661</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176903</t>
+          <t xml:space="preserve">311176904</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmosevej 7</t>
+          <t xml:space="preserve">Mosegårdsvej 7A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4394661</t>
+          <t xml:space="preserve">4395005</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J51">
-        <v>545</v>
+        <v>325</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176904</t>
+          <t xml:space="preserve">311176902</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7A</t>
+          <t xml:space="preserve">Mosegårdsvej 7F</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7F</t>
+          <t xml:space="preserve">Mosegårdsvej 7L</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7L</t>
+          <t xml:space="preserve">Mosegårdsvej 7Q</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J54">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 7Q</t>
+          <t xml:space="preserve">Tingvejen 22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4395005</t>
+          <t xml:space="preserve">100009904</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>325</v>
+        <v>1450</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176902</t>
+          <t xml:space="preserve">311176899</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 22</t>
+          <t xml:space="preserve">Ullerupdalvej 233</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100009904</t>
+          <t xml:space="preserve">5671590</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>1450</v>
+        <v>362</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176899</t>
+          <t xml:space="preserve">311177404</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-17</t>
+          <t xml:space="preserve">2026-05-19</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupdalvej 233</t>
+          <t xml:space="preserve">Øster Voldgade 3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671590</t>
+          <t xml:space="preserve">5665369</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>362</v>
+        <v>1571</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177404</t>
+          <t xml:space="preserve">311179613</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-19</t>
+          <t xml:space="preserve">2026-05-30</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 3</t>
+          <t xml:space="preserve">Damvej 1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665369</t>
+          <t xml:space="preserve">5669794</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>1571</v>
+        <v>634</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179613</t>
+          <t xml:space="preserve">311179816</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 1</t>
+          <t xml:space="preserve">Havepladsvej 175</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5669794</t>
+          <t xml:space="preserve">5666167</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>634</v>
+        <v>6463</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179816</t>
+          <t xml:space="preserve">311179818</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 175</t>
+          <t xml:space="preserve">Havepladsvej 177</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havepladsvej 177</t>
+          <t xml:space="preserve">Taulov Kirkevej 35A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,20 +4551,20 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666167</t>
+          <t xml:space="preserve">7077980</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J61">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179818</t>
+          <t xml:space="preserve">311180015</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J62">
-        <v>350</v>
+        <v>579</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J63">
-        <v>579</v>
+        <v>967</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4781,11 +4781,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J66">
-        <v>903</v>
+        <v>3257</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taulov Kirkevej 35A</t>
+          <t xml:space="preserve">Herfordparken 1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7077980</t>
+          <t xml:space="preserve">100040538</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>3257</v>
+        <v>12410</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311180015</t>
+          <t xml:space="preserve">311183512</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herfordparken 1</t>
+          <t xml:space="preserve">Højdedraget 1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040538</t>
+          <t xml:space="preserve">4398224</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="J68">
-        <v>12410</v>
+        <v>1697</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183512</t>
+          <t xml:space="preserve">311183515</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højdedraget 1</t>
+          <t xml:space="preserve">Højdedraget 2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398224</t>
+          <t xml:space="preserve">4398311</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>1697</v>
+        <v>445</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183515</t>
+          <t xml:space="preserve">311183342</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højdedraget 2</t>
+          <t xml:space="preserve">Kongensgade 9A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398311</t>
+          <t xml:space="preserve">5664154</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J70">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183342</t>
+          <t xml:space="preserve">311183444</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 9A</t>
+          <t xml:space="preserve">Lyngsoddevej 5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664154</t>
+          <t xml:space="preserve">4393805</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>438</v>
+        <v>705</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183444</t>
+          <t xml:space="preserve">311183505</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngsoddevej 5</t>
+          <t xml:space="preserve">Skolesvinget 3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4393805</t>
+          <t xml:space="preserve">4391810</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>705</v>
+        <v>2500</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183505</t>
+          <t xml:space="preserve">311183359</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5456,11 +5456,11 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J73">
-        <v>2500</v>
+        <v>1546</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 3</t>
+          <t xml:space="preserve">Skolesvinget 7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,15 +5531,15 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J74">
-        <v>1546</v>
+        <v>324</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183402</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 7</t>
+          <t xml:space="preserve">Søndermarksvej 130</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4391810</t>
+          <t xml:space="preserve">7489049</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>324</v>
+        <v>1101</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183402</t>
+          <t xml:space="preserve">311183409</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndermarksvej 130</t>
+          <t xml:space="preserve">Anders Billes Vej 26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489049</t>
+          <t xml:space="preserve">5669032</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J76">
-        <v>1101</v>
+        <v>266</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183409</t>
+          <t xml:space="preserve">311183604</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Billes Vej 26</t>
+          <t xml:space="preserve">Jupitervej 29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5669032</t>
+          <t xml:space="preserve">5666595</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183604</t>
+          <t xml:space="preserve">311183598</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 29</t>
+          <t xml:space="preserve">Bøgeskovvej 37B</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666595</t>
+          <t xml:space="preserve">5673910</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
-        <v>276</v>
+        <v>1759</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183598</t>
+          <t xml:space="preserve">311184758</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-16</t>
+          <t xml:space="preserve">2026-06-21</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J79">
-        <v>1759</v>
+        <v>866</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgeskovvej 37B</t>
+          <t xml:space="preserve">Jacob Hansens Vej 5A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5673910</t>
+          <t xml:space="preserve">1805168</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>866</v>
+        <v>1032</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184758</t>
+          <t xml:space="preserve">311184719</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Hansens Vej 5A</t>
+          <t xml:space="preserve">Jeppe Aakjærs Vej 2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805168</t>
+          <t xml:space="preserve">5668776</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>1032</v>
+        <v>342</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184719</t>
+          <t xml:space="preserve">311184747</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeppe Aakjærs Vej 2</t>
+          <t xml:space="preserve">Jupitervej 30A</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668776</t>
+          <t xml:space="preserve">5666593</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184747</t>
+          <t xml:space="preserve">311190979</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-21</t>
+          <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30A</t>
+          <t xml:space="preserve">Tingvejen 31</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666593</t>
+          <t xml:space="preserve">4397145</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>311</v>
+        <v>7774</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190979</t>
+          <t xml:space="preserve">311190960</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 31</t>
+          <t xml:space="preserve">Dronningensgade 66</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4397145</t>
+          <t xml:space="preserve">5664362</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>7774</v>
+        <v>456</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190960</t>
+          <t xml:space="preserve">311191251</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-20</t>
+          <t xml:space="preserve">2026-07-22</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 66</t>
+          <t xml:space="preserve">Egumvej 52</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664362</t>
+          <t xml:space="preserve">8012611</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>456</v>
+        <v>733</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191251</t>
+          <t xml:space="preserve">311191300</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egumvej 52</t>
+          <t xml:space="preserve">Jupitervej 30B</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8012611</t>
+          <t xml:space="preserve">5666593</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>733</v>
+        <v>386</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191300</t>
+          <t xml:space="preserve">311192450</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-22</t>
+          <t xml:space="preserve">2026-08-01</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30B</t>
+          <t xml:space="preserve">Jupitervej 30C</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6506,15 +6506,15 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192450</t>
+          <t xml:space="preserve">311192453</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervej 30C</t>
+          <t xml:space="preserve">Nørre Allé 1A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5666593</t>
+          <t xml:space="preserve">5671168</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J88">
-        <v>383</v>
+        <v>882</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192453</t>
+          <t xml:space="preserve">311192396</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 1A</t>
+          <t xml:space="preserve">Nørre Allé 3A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>882</v>
+        <v>1007</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 3A</t>
+          <t xml:space="preserve">Prangervej 2A</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671168</t>
+          <t xml:space="preserve">5665886</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J90">
-        <v>1007</v>
+        <v>1708</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192396</t>
+          <t xml:space="preserve">311192422</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6806,15 +6806,15 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J91">
-        <v>1708</v>
+        <v>1079</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192422</t>
+          <t xml:space="preserve">311192419</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prangervej 2A</t>
+          <t xml:space="preserve">Erritsø Bygade 85A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665886</t>
+          <t xml:space="preserve">324492, 324493, 324494</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>1079</v>
+        <v>4772</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192419</t>
+          <t xml:space="preserve">311192568</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-01</t>
+          <t xml:space="preserve">2026-08-02</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 85A</t>
+          <t xml:space="preserve">Gothersgade 20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">324492, 324493, 324494</t>
+          <t xml:space="preserve">7308352</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>4772</v>
+        <v>11624</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192568</t>
+          <t xml:space="preserve">311192535</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gothersgade 20</t>
+          <t xml:space="preserve">Krogsagervej 30A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7308352</t>
+          <t xml:space="preserve">4395059</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>11624</v>
+        <v>9936</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192535</t>
+          <t xml:space="preserve">311192576</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogsagervej 30A</t>
+          <t xml:space="preserve">Prinsessegade 29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4395059</t>
+          <t xml:space="preserve">5664659</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>9936</v>
+        <v>1404</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192576</t>
+          <t xml:space="preserve">311192540</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsessegade 29</t>
+          <t xml:space="preserve">Randalsvej 51</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664659</t>
+          <t xml:space="preserve">5671426</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J96">
-        <v>1404</v>
+        <v>686</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192540</t>
+          <t xml:space="preserve">311294175</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randalsvej 51</t>
+          <t xml:space="preserve">Indre Ringvej 173A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671426</t>
+          <t xml:space="preserve">5672317</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,11 +7260,11 @@
         </is>
       </c>
       <c r="J97">
-        <v>686</v>
+        <v>1640</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294175</t>
+          <t xml:space="preserve">311193728</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-02</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indre Ringvej 173A</t>
+          <t xml:space="preserve">Indre Ringvej 175</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J98">
-        <v>1640</v>
+        <v>695</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J99">
-        <v>695</v>
+        <v>358</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J100">
-        <v>358</v>
+        <v>3300</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7556,11 +7556,11 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J101">
-        <v>3300</v>
+        <v>499</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J102">
-        <v>499</v>
+        <v>3364</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indre Ringvej 175</t>
+          <t xml:space="preserve">Skansevej 51</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J103">
-        <v>3364</v>
+        <v>1676</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 51</t>
+          <t xml:space="preserve">Prinsessegade 27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5672317</t>
+          <t xml:space="preserve">5664658</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>1676</v>
+        <v>5773</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193728</t>
+          <t xml:space="preserve">311194185</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsessegade 27</t>
+          <t xml:space="preserve">Vendersgade 49</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664658</t>
+          <t xml:space="preserve">5663493</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>5773</v>
+        <v>3590</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194185</t>
+          <t xml:space="preserve">311194928</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 49</t>
+          <t xml:space="preserve">Erritsø Bygade 85B</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5663493</t>
+          <t xml:space="preserve">324490, 324491</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>3590</v>
+        <v>1750</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194928</t>
+          <t xml:space="preserve">311199931</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-17</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 85B</t>
+          <t xml:space="preserve">Gl. Landevej 45</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">324490, 324491</t>
+          <t xml:space="preserve">4394923</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>1750</v>
+        <v>958</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199931</t>
+          <t xml:space="preserve">311199890</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 45</t>
+          <t xml:space="preserve">Købmagergade 40</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4394923</t>
+          <t xml:space="preserve">1809125</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>958</v>
+        <v>2418</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199890</t>
+          <t xml:space="preserve">311199920</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Købmagergade 40</t>
+          <t xml:space="preserve">Vendersgade 4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809125</t>
+          <t xml:space="preserve">100075274</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>2418</v>
+        <v>5956</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199920</t>
+          <t xml:space="preserve">311199924</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 4</t>
+          <t xml:space="preserve">Vendersgade 43</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100075274</t>
+          <t xml:space="preserve">327334, 327335</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>5956</v>
+        <v>2436</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199924</t>
+          <t xml:space="preserve">311199903</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 43</t>
+          <t xml:space="preserve">Høgevej 5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">327334, 327335</t>
+          <t xml:space="preserve">5668622</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>2436</v>
+        <v>6177</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199903</t>
+          <t xml:space="preserve">311200238</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J112">
-        <v>6177</v>
+        <v>607</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J113">
-        <v>607</v>
+        <v>505</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
-        <v>505</v>
+        <v>605</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J115">
-        <v>605</v>
+        <v>859</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 5</t>
+          <t xml:space="preserve">Højmosevej 2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668622</t>
+          <t xml:space="preserve">8730679</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>859</v>
+        <v>4305</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200238</t>
+          <t xml:space="preserve">311200242</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmosevej 2</t>
+          <t xml:space="preserve">Norgesgade 46A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730679</t>
+          <t xml:space="preserve">5665460</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>4305</v>
+        <v>1912</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200242</t>
+          <t xml:space="preserve">311200227</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesgade 46A</t>
+          <t xml:space="preserve">Prangervej 7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665460</t>
+          <t xml:space="preserve">5665118</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>1912</v>
+        <v>1159</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200227</t>
+          <t xml:space="preserve">311200210</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J119">
-        <v>1159</v>
+        <v>1107</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200210</t>
+          <t xml:space="preserve">311200127</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8981,15 +8981,15 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J120">
-        <v>1107</v>
+        <v>648</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200127</t>
+          <t xml:space="preserve">311200129</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prangervej 7</t>
+          <t xml:space="preserve">Viaduktvej 9A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5665118</t>
+          <t xml:space="preserve">7429396</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>648</v>
+        <v>2343</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200129</t>
+          <t xml:space="preserve">311200122</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 9A</t>
+          <t xml:space="preserve">Industrivej 8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7429396</t>
+          <t xml:space="preserve">5671399</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J122">
-        <v>2343</v>
+        <v>395</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200122</t>
+          <t xml:space="preserve">311200731</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9206,11 +9206,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J123">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 8</t>
+          <t xml:space="preserve">Kongensgade 111</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,25 +9276,25 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671399</t>
+          <t xml:space="preserve">8566948</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>284</v>
+        <v>5566</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200731</t>
+          <t xml:space="preserve">311200752</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 111</t>
+          <t xml:space="preserve">Røde Banke 73</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8566948</t>
+          <t xml:space="preserve">4392814</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,16 +9360,16 @@
         </is>
       </c>
       <c r="J125">
-        <v>5566</v>
+        <v>424</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200752</t>
+          <t xml:space="preserve">311200762</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røde Banke 73</t>
+          <t xml:space="preserve">Erritsø Bygade 15A</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4392814</t>
+          <t xml:space="preserve">4392366</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>424</v>
+        <v>2517</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200762</t>
+          <t xml:space="preserve">311202290</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erritsø Bygade 15A</t>
+          <t xml:space="preserve">Skjoldborgsvej 21</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4392366</t>
+          <t xml:space="preserve">5668856</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>2517</v>
+        <v>5092</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202290</t>
+          <t xml:space="preserve">311202296</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldborgsvej 21</t>
+          <t xml:space="preserve">Trelde Næsvej 300</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5668856</t>
+          <t xml:space="preserve">9712209</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>5092</v>
+        <v>347</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202296</t>
+          <t xml:space="preserve">311202310</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trelde Næsvej 300</t>
+          <t xml:space="preserve">Øster Voldgade 18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9712209</t>
+          <t xml:space="preserve">5664300</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>347</v>
+        <v>6219</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202310</t>
+          <t xml:space="preserve">311202427</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9679,12 +9679,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9731,11 +9731,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>6219</v>
+        <v>1170</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9806,11 +9806,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J131">
-        <v>1170</v>
+        <v>4140</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9829,12 +9829,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9881,11 +9881,11 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J132">
-        <v>4140</v>
+        <v>775</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9904,12 +9904,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J133">
-        <v>775</v>
+        <v>474</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18</t>
+          <t xml:space="preserve">Øster Voldgade 18M</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J134">
-        <v>474</v>
+        <v>362</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18M</t>
+          <t xml:space="preserve">Øster Voldgade 18N</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J135">
-        <v>362</v>
+        <v>800</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Voldgade 18N</t>
+          <t xml:space="preserve">Frantz Hansens Allé 1B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5664300</t>
+          <t xml:space="preserve">8730871</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J136">
-        <v>800</v>
+        <v>269</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202427</t>
+          <t xml:space="preserve">311203335</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,17 +10199,17 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantz Hansens Allé 1B</t>
+          <t xml:space="preserve">Vigøvej 2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730871</t>
+          <t xml:space="preserve">4397347</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>269</v>
+        <v>650</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203335</t>
+          <t xml:space="preserve">311203339</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigøvej 2</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4397347</t>
+          <t xml:space="preserve">4396768</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>650</v>
+        <v>2227</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203339</t>
+          <t xml:space="preserve">311203417</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,17 +10349,17 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Ullerupdalvej 10A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4396768</t>
+          <t xml:space="preserve">5671171</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J139">
-        <v>2227</v>
+        <v>1187</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203417</t>
+          <t xml:space="preserve">311204999</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerupdalvej 10A</t>
+          <t xml:space="preserve">Vestre Ringvej 100</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671171</t>
+          <t xml:space="preserve">9936679</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>1187</v>
+        <v>12573</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204999</t>
+          <t xml:space="preserve">311206580</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>12573</v>
+        <v>5071</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J142">
-        <v>5071</v>
+        <v>4464</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J143">
-        <v>4464</v>
+        <v>1375</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Ringvej 100</t>
+          <t xml:space="preserve">Nørre Allé 5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,20 +10776,20 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9936679</t>
+          <t xml:space="preserve">5671171</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>1375</v>
+        <v>12418</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206580</t>
+          <t xml:space="preserve">311213911</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 5</t>
+          <t xml:space="preserve">Dronningensgade 95</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,30 +10851,30 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5671171</t>
+          <t xml:space="preserve">7260988</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J145">
-        <v>12418</v>
+        <v>302</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213911</t>
+          <t xml:space="preserve">311340255</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 95</t>
+          <t xml:space="preserve">Dronningensgade 97A</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>302</v>
+        <v>4611</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J147">
-        <v>4611</v>
+        <v>10047</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J148">
-        <v>10047</v>
+        <v>701</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97A</t>
+          <t xml:space="preserve">Dronningensgade 97B</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J149">
-        <v>701</v>
+        <v>7973</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97B</t>
+          <t xml:space="preserve">Dronningensgade 97E</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J150">
-        <v>7973</v>
+        <v>1083</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97E</t>
+          <t xml:space="preserve">Dronningensgade 97F</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J151">
-        <v>1083</v>
+        <v>940</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 97F</t>
+          <t xml:space="preserve">Sjællandsgade 108</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J152">
-        <v>940</v>
+        <v>1042</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsgade 108</t>
+          <t xml:space="preserve">Industrivej 26</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260988</t>
+          <t xml:space="preserve">7120196</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>1042</v>
+        <v>1996</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340255</t>
+          <t xml:space="preserve">311512465</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">BYGTEST ApS</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 26</t>
+          <t xml:space="preserve">Vestre Ringvej 101</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7120196</t>
+          <t xml:space="preserve">1509827</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="J154">
-        <v>1996</v>
+        <v>30856</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512465</t>
+          <t xml:space="preserve">311731153</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">BYGTEST ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-15</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11606,15 +11606,15 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>30856</v>
+        <v>3066</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731153</t>
+          <t xml:space="preserve">311731047</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Ringvej 101</t>
+          <t xml:space="preserve">Madsbyvej 6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,30 +11676,30 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1509827</t>
+          <t xml:space="preserve">8730852</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J156">
-        <v>3066</v>
+        <v>832</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731047</t>
+          <t xml:space="preserve">311786875</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2034-09-24</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madsbyvej 6</t>
+          <t xml:space="preserve">Vester Voldgade 19A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,30 +11751,30 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730852</t>
+          <t xml:space="preserve">8635786</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>832</v>
+        <v>594</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786872</t>
+          <t xml:space="preserve">311928459</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-24</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">

--- a/public/exports/69116418.xlsx
+++ b/public/exports/69116418.xlsx
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166041</t>
+          <t xml:space="preserve">311166039</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183359</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183402</t>
+          <t xml:space="preserve">311183354</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
